--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334662</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334681</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334655</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334659</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334664</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334677</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334679</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334678</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334676</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334680</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332388</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332400</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332402</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334646</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334666</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334668</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334638</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334641</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334650</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334669</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3447,6 +3572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334643</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3558,6 +3688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332393</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3669,6 +3804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332397</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3780,6 +3920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332403</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3891,6 +4036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332409</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4002,6 +4152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332412</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4113,6 +4268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332414</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4224,6 +4384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332415</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4335,6 +4500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334644</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4446,6 +4616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334648</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4557,6 +4732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334657</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4668,6 +4848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334660</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4779,6 +4964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334673</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4890,6 +5080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332399</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5001,6 +5196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334653</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5112,6 +5312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334665</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5223,6 +5428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334671</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5334,6 +5544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334672</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5450,6 +5665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332387</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5566,6 +5786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332394</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5682,6 +5907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332396</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5798,6 +6028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334640</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5914,6 +6149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334651</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6028,6 +6268,11 @@
       <c r="AY49" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334682</t>
         </is>
       </c>
     </row>
@@ -6150,6 +6395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332411</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6274,6 +6524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332391</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6398,6 +6653,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332392</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6509,6 +6769,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332406</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6620,6 +6885,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332398</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6731,6 +7001,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332404</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6842,6 +7117,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332410</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6953,6 +7233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334649</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7064,6 +7349,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334656</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7175,6 +7465,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334674</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7286,6 +7581,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332395</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7397,6 +7697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334667</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7508,6 +7813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332401</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7619,6 +7929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332405</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7730,6 +8045,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332407</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7841,6 +8161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332413</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7952,6 +8277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334633</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8063,6 +8393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334634</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8174,6 +8509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334636</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8285,6 +8625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334639</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8396,6 +8741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334642</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8507,6 +8857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334647</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8618,6 +8973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334652</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8729,6 +9089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334658</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8840,8 +9205,88 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135334663</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135334662</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92235</v>
+        <v>92277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135334655</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135334637</v>
       </c>
       <c r="B5" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135334661</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135334635</v>
       </c>
       <c r="B7" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135334654</v>
       </c>
       <c r="B8" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135334659</v>
       </c>
       <c r="B9" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135334664</v>
       </c>
       <c r="B10" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135334677</v>
       </c>
       <c r="B11" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135334679</v>
       </c>
       <c r="B12" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135334678</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135334676</v>
       </c>
       <c r="B14" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135334680</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135332388</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135332400</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>135332402</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>135334646</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>135334666</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>135334668</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135334638</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>135334641</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>135334650</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>135334669</v>
       </c>
       <c r="B25" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>135334643</v>
       </c>
       <c r="B26" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>135332393</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>135332397</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>135332403</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135332409</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135332412</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>135332414</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>135332415</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135334644</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>135334648</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>135334657</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>135334660</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>135334673</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135332399</v>
       </c>
       <c r="B39" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>135334653</v>
       </c>
       <c r="B40" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>135334665</v>
       </c>
       <c r="B41" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>135334671</v>
       </c>
       <c r="B42" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>135334672</v>
       </c>
       <c r="B43" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>135332387</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>135332394</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>135332396</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>135334640</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>135334651</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135334682</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135332411</v>
       </c>
       <c r="B50" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135332391</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135332392</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>135332406</v>
       </c>
       <c r="B53" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>135332398</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>135332404</v>
       </c>
       <c r="B55" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135332410</v>
       </c>
       <c r="B56" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135334649</v>
       </c>
       <c r="B57" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135334656</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>135334674</v>
       </c>
       <c r="B59" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>135332395</v>
       </c>
       <c r="B60" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>135334667</v>
       </c>
       <c r="B61" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>135332401</v>
       </c>
       <c r="B62" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>135332405</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>135332407</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>135332413</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>135334633</v>
       </c>
       <c r="B66" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>135334634</v>
       </c>
       <c r="B67" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>135334636</v>
       </c>
       <c r="B68" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>135334639</v>
       </c>
       <c r="B69" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135334642</v>
       </c>
       <c r="B70" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>135334647</v>
       </c>
       <c r="B71" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>135334652</v>
       </c>
       <c r="B72" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>135334658</v>
       </c>
       <c r="B73" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135334663</v>
       </c>
       <c r="B74" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135334662</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92277</v>
+        <v>92304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135334655</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135334637</v>
       </c>
       <c r="B5" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135334661</v>
       </c>
       <c r="B6" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135334635</v>
       </c>
       <c r="B7" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135334654</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135334659</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135334664</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135334677</v>
       </c>
       <c r="B11" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135334679</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135334678</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135334676</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135334680</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>135332388</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135332400</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>135332402</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>135334646</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>135334666</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>135334668</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135334638</v>
       </c>
       <c r="B22" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>135334641</v>
       </c>
       <c r="B23" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>135334650</v>
       </c>
       <c r="B24" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>135334669</v>
       </c>
       <c r="B25" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>135334643</v>
       </c>
       <c r="B26" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>135332393</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>135332397</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>135332403</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135332409</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>135332412</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>135332414</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>135332415</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>135334644</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>135334648</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>135334657</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>135334660</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>135334673</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135332399</v>
       </c>
       <c r="B39" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>135334653</v>
       </c>
       <c r="B40" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>135334665</v>
       </c>
       <c r="B41" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>135334671</v>
       </c>
       <c r="B42" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>135334672</v>
       </c>
       <c r="B43" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135332391</v>
       </c>
       <c r="B51" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135332392</v>
       </c>
       <c r="B52" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>135332406</v>
       </c>
       <c r="B53" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>135332398</v>
       </c>
       <c r="B54" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>135332404</v>
       </c>
       <c r="B55" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>135332410</v>
       </c>
       <c r="B56" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135334649</v>
       </c>
       <c r="B57" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135334656</v>
       </c>
       <c r="B58" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>135334674</v>
       </c>
       <c r="B59" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>135332395</v>
       </c>
       <c r="B60" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>135334667</v>
       </c>
       <c r="B61" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>135332401</v>
       </c>
       <c r="B62" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>135332405</v>
       </c>
       <c r="B63" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>135332407</v>
       </c>
       <c r="B64" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>135332413</v>
       </c>
       <c r="B65" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>135334633</v>
       </c>
       <c r="B66" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>135334634</v>
       </c>
       <c r="B67" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>135334636</v>
       </c>
       <c r="B68" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>135334639</v>
       </c>
       <c r="B69" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135334642</v>
       </c>
       <c r="B70" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>135334647</v>
       </c>
       <c r="B71" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>135334652</v>
       </c>
       <c r="B72" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>135334658</v>
       </c>
       <c r="B73" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135334663</v>
       </c>
       <c r="B74" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 30617-2025 artfynd.xlsx
+++ b/artfynd/A 30617-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135334662</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135334681</v>
       </c>
       <c r="B3" t="n">
-        <v>92309</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135334661</v>
       </c>
       <c r="B6" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135334635</v>
       </c>
       <c r="B7" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135334654</v>
       </c>
       <c r="B8" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135334659</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135334664</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135334677</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135334679</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135334678</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135334676</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>135334680</v>
       </c>
       <c r="B15" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135332391</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135332392</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>135332406</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
